--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3168907</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F5">
-        <v>1674</v>
+        <v>436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168907</t>
+          <t xml:space="preserve">3177919, 100507701</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F6">
-        <v>436</v>
+        <v>3596</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F7">
-        <v>684</v>
+        <v>446</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177919, 100507701</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F8">
-        <v>3596</v>
+        <v>926</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">402929, 402930</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>446</v>
+        <v>874</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">403345, 403346</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>926</v>
+        <v>1366</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524988</t>
+          <t xml:space="preserve">407002</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>335</v>
+        <v>1091</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F12">
-        <v>598</v>
+        <v>518</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F13">
-        <v>1490</v>
+        <v>1132</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">409430, 409431</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>1992</v>
+        <v>7175</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">428228, 428229, 428230</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>656</v>
+        <v>3279</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">5524988</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>3761</v>
+        <v>335</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>801</v>
+        <v>1490</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F36">
-        <v>1934</v>
+        <v>1674</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053550</t>
+          <t xml:space="preserve">200051322</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-04</t>
+          <t xml:space="preserve">2021-07-13</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="F37">
-        <v>480</v>
+        <v>1934</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054733</t>
+          <t xml:space="preserve">200053550</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2021-10-04</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526510</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="F38">
-        <v>258</v>
+        <v>480</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054944</t>
+          <t xml:space="preserve">200054733</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-17</t>
+          <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">5526510</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>779</v>
+        <v>258</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055336</t>
+          <t xml:space="preserve">200054944</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2021-11-17</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1986,20 +1986,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F40">
-        <v>852</v>
+        <v>779</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055336</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2036,11 +2036,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>470</v>
+        <v>852</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F42">
-        <v>1347</v>
+        <v>470</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2136,11 +2136,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F43">
-        <v>422</v>
+        <v>1347</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2186,11 +2186,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F44">
-        <v>575</v>
+        <v>422</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,20 +2231,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F45">
-        <v>394</v>
+        <v>575</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>585</v>
+        <v>394</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F47">
-        <v>1647</v>
+        <v>585</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150176</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
-        <v>499</v>
+        <v>1647</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055998</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169983</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F49">
-        <v>5060</v>
+        <v>1992</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056002</t>
+          <t xml:space="preserve">200055924</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">403345, 403346</t>
+          <t xml:space="preserve">3150176</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>1366</v>
+        <v>499</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056210</t>
+          <t xml:space="preserve">200055998</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-21</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980081</t>
+          <t xml:space="preserve">3169983</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>560</v>
+        <v>5060</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311044984</t>
+          <t xml:space="preserve">200056198</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-26</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">753473, 3217725</t>
+          <t xml:space="preserve">9980081</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F52">
-        <v>1765</v>
+        <v>560</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311069618</t>
+          <t xml:space="preserve">311044984</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-22</t>
+          <t xml:space="preserve">2024-03-26</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178967</t>
+          <t xml:space="preserve">753473, 3217725</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F53">
-        <v>1631</v>
+        <v>1765</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144273</t>
+          <t xml:space="preserve">311126737</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2025-07-29</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,35 +2681,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521204</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F54">
-        <v>4153</v>
+        <v>656</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213844</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521383</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F55">
-        <v>1332</v>
+        <v>3761</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224295</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-24</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2781,35 +2781,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159619</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F56">
-        <v>3719</v>
+        <v>801</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466015</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2831,35 +2831,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">3178967</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>1395</v>
+        <v>1631</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311175796</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2026-05-11</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">5521204</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>2086</v>
+        <v>4153</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311213844</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">5521383</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>1240</v>
+        <v>1332</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311224295</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,20 +2981,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">3159619</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>1325</v>
+        <v>3719</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466015</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>2005</v>
+        <v>1395</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3086,15 +3086,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F62">
-        <v>1055</v>
+        <v>598</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466011</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3131,20 +3131,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F63">
-        <v>2764</v>
+        <v>2086</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3181,20 +3181,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F64">
-        <v>1021</v>
+        <v>1240</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,20 +3231,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F65">
-        <v>4161</v>
+        <v>1325</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3281,20 +3281,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F66">
-        <v>808</v>
+        <v>2005</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F67">
-        <v>3691</v>
+        <v>1055</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F68">
-        <v>1680</v>
+        <v>2764</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>1073</v>
+        <v>1021</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>1780</v>
+        <v>4161</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507102</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F71">
-        <v>6875</v>
+        <v>808</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477652</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>717</v>
+        <v>3691</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>2644</v>
+        <v>1680</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477664</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F74">
-        <v>842</v>
+        <v>1073</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F75">
-        <v>919</v>
+        <v>1780</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">1507102</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>495</v>
+        <v>6875</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311477652</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F77">
-        <v>1088</v>
+        <v>717</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F78">
-        <v>464</v>
+        <v>2644</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485016</t>
+          <t xml:space="preserve">311477664</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170022</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,11 +3940,11 @@
         </is>
       </c>
       <c r="F79">
-        <v>3071</v>
+        <v>842</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485008</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3981,20 +3981,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>1477</v>
+        <v>919</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485012</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4031,20 +4031,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F81">
-        <v>1933</v>
+        <v>495</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485012</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4081,20 +4081,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F82">
-        <v>966</v>
+        <v>1088</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4131,20 +4131,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F83">
-        <v>1942</v>
+        <v>464</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485016</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,20 +4181,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3170022</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>634</v>
+        <v>3071</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485008</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4231,20 +4231,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>1974</v>
+        <v>1477</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,20 +4281,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F86">
-        <v>668</v>
+        <v>1933</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3210318</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="F87">
-        <v>785</v>
+        <v>684</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485005</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4381,20 +4381,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524762</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F88">
-        <v>8112</v>
+        <v>966</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485007</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F89">
-        <v>534</v>
+        <v>1942</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485121</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F90">
-        <v>528</v>
+        <v>634</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F91">
-        <v>941</v>
+        <v>1974</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F92">
-        <v>2112</v>
+        <v>668</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3210318</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F93">
-        <v>458</v>
+        <v>785</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485005</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">5524762</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>602</v>
+        <v>8112</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485007</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,20 +4731,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F95">
-        <v>393</v>
+        <v>534</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485121</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4786,11 +4786,11 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>440</v>
+        <v>528</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4836,11 +4836,11 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F97">
-        <v>812</v>
+        <v>941</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4886,11 +4886,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F98">
-        <v>406</v>
+        <v>2112</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4936,11 +4936,11 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F99">
-        <v>1230</v>
+        <v>458</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F100">
-        <v>946</v>
+        <v>602</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5036,11 +5036,11 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F101">
-        <v>1206</v>
+        <v>393</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F102">
-        <v>269</v>
+        <v>440</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494580</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F103">
-        <v>415</v>
+        <v>812</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494581</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800309</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F104">
-        <v>549</v>
+        <v>406</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494569</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105">
-        <v>2334</v>
+        <v>1230</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F106">
-        <v>3417</v>
+        <v>946</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F107">
-        <v>1399</v>
+        <v>1206</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494556</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,20 +5381,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F108">
-        <v>349</v>
+        <v>269</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5431,20 +5431,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F109">
-        <v>886</v>
+        <v>415</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494581</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">1800309</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>430</v>
+        <v>549</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494569</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,20 +5531,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>507</v>
+        <v>2334</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5581,20 +5581,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168485</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F112">
-        <v>669</v>
+        <v>3417</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494573</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5631,20 +5631,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204366</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F113">
-        <v>536</v>
+        <v>1399</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494576</t>
+          <t xml:space="preserve">311494556</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,11 +5690,11 @@
         </is>
       </c>
       <c r="F114">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5731,20 +5731,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>1336</v>
+        <v>886</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5781,20 +5781,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F116">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5831,20 +5831,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527621</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F117">
-        <v>381</v>
+        <v>507</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494568</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527904</t>
+          <t xml:space="preserve">3168485</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,11 +5890,11 @@
         </is>
       </c>
       <c r="F118">
-        <v>586</v>
+        <v>669</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494579</t>
+          <t xml:space="preserve">311494573</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7881176</t>
+          <t xml:space="preserve">3204366</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,11 +5940,11 @@
         </is>
       </c>
       <c r="F119">
-        <v>760</v>
+        <v>536</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494575</t>
+          <t xml:space="preserve">311494576</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719671</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5990,11 +5990,11 @@
         </is>
       </c>
       <c r="F120">
-        <v>707</v>
+        <v>393</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494577</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9797238</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,11 +6040,11 @@
         </is>
       </c>
       <c r="F121">
-        <v>766</v>
+        <v>1336</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494566</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F122">
-        <v>8698</v>
+        <v>455</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">5527621</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>1003</v>
+        <v>381</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311494568</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100218261</t>
+          <t xml:space="preserve">5527904</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>8190</v>
+        <v>586</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566030</t>
+          <t xml:space="preserve">311494579</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178968</t>
+          <t xml:space="preserve">7881176</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625072</t>
+          <t xml:space="preserve">311494575</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526859</t>
+          <t xml:space="preserve">8719671</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>2155</v>
+        <v>707</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650741</t>
+          <t xml:space="preserve">311494577</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522955</t>
+          <t xml:space="preserve">9797238</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>2615</v>
+        <v>766</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669639</t>
+          <t xml:space="preserve">311494566</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507298</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="F128">
-        <v>395</v>
+        <v>8698</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674591</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218381</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F129">
-        <v>299</v>
+        <v>1003</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790590</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100606984</t>
+          <t xml:space="preserve">100218261</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6490,16 +6490,16 @@
         </is>
       </c>
       <c r="F130">
-        <v>10174</v>
+        <v>8190</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794226</t>
+          <t xml:space="preserve">311566030</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-29</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162830</t>
+          <t xml:space="preserve">3178968</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>432</v>
+        <v>751</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885642</t>
+          <t xml:space="preserve">311625072</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178136</t>
+          <t xml:space="preserve">5526859</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>278</v>
+        <v>2155</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885633</t>
+          <t xml:space="preserve">311650741</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">5522955</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F133">
-        <v>515</v>
+        <v>2615</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885634</t>
+          <t xml:space="preserve">311669639</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217023</t>
+          <t xml:space="preserve">1507298</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>269</v>
+        <v>395</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885687</t>
+          <t xml:space="preserve">311674591</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">3218381</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6740,16 +6740,16 @@
         </is>
       </c>
       <c r="F135">
-        <v>2230</v>
+        <v>299</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885676</t>
+          <t xml:space="preserve">311790590</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">100606984</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136">
-        <v>1492</v>
+        <v>10174</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885677</t>
+          <t xml:space="preserve">311794226</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">402929, 402930</t>
+          <t xml:space="preserve">3162830</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,11 +6840,11 @@
         </is>
       </c>
       <c r="F137">
-        <v>874</v>
+        <v>432</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885675</t>
+          <t xml:space="preserve">311885642</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521240</t>
+          <t xml:space="preserve">3178136</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="F138">
-        <v>473</v>
+        <v>278</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885656</t>
+          <t xml:space="preserve">311885633</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6931,20 +6931,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521462</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F139">
-        <v>667</v>
+        <v>515</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885657</t>
+          <t xml:space="preserve">311885634</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521521</t>
+          <t xml:space="preserve">3217023</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,11 +6990,11 @@
         </is>
       </c>
       <c r="F140">
-        <v>3681</v>
+        <v>269</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885649</t>
+          <t xml:space="preserve">311885687</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527785</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7040,11 +7040,11 @@
         </is>
       </c>
       <c r="F141">
-        <v>4178</v>
+        <v>2230</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885653</t>
+          <t xml:space="preserve">311885676</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808737</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>402</v>
+        <v>1492</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886408</t>
+          <t xml:space="preserve">311885677</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">5521240</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>256</v>
+        <v>473</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311885656</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">5521462</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>382</v>
+        <v>667</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311885657</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7201111</t>
+          <t xml:space="preserve">5521521</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,16 +7240,16 @@
         </is>
       </c>
       <c r="F145">
-        <v>494</v>
+        <v>3681</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886401</t>
+          <t xml:space="preserve">311885649</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214506</t>
+          <t xml:space="preserve">5527785</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F146">
-        <v>4371</v>
+        <v>4178</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886892</t>
+          <t xml:space="preserve">311885653</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214536</t>
+          <t xml:space="preserve">1808737</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>820</v>
+        <v>402</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886893</t>
+          <t xml:space="preserve">311886408</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">428228, 428229, 428230</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="F148">
-        <v>3279</v>
+        <v>256</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886888</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F149">
-        <v>1091</v>
+        <v>382</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887712</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">7201111</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887713</t>
+          <t xml:space="preserve">311886401</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3214506</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>1132</v>
+        <v>4371</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887715</t>
+          <t xml:space="preserve">311886892</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3214536</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>265</v>
+        <v>820</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888133</t>
+          <t xml:space="preserve">311886893</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7636,15 +7636,15 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>393</v>
+        <v>265</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888130</t>
+          <t xml:space="preserve">311888133</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F154">
-        <v>1086</v>
+        <v>393</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888130</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7736,11 +7736,11 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F155">
-        <v>994</v>
+        <v>1086</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7786,11 +7786,11 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F156">
-        <v>611</v>
+        <v>994</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7831,20 +7831,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">409430, 409431</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F157">
-        <v>7175</v>
+        <v>611</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888761</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894481</t>
+          <t xml:space="preserve">311894479</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">

--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børge Christensens V 12</t>
+          <t xml:space="preserve">Asdalvej 16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014113</t>
+          <t xml:space="preserve">8719163</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H2">
-        <v>333</v>
+        <v>1761</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 5</t>
+          <t xml:space="preserve">Baggesvognsvej 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100450176</t>
+          <t xml:space="preserve">9043261</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>528</v>
+        <v>418</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25</t>
+          <t xml:space="preserve">Baggesvognsvej 57A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">9598787</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H4">
-        <v>429</v>
+        <v>360</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 184</t>
+          <t xml:space="preserve">Bodøvej 13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168907</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H5">
-        <v>436</v>
+        <v>1980</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willemoesvej 4</t>
+          <t xml:space="preserve">Børge Christensens V 12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177919, 100507701</t>
+          <t xml:space="preserve">10014113</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H6">
-        <v>3596</v>
+        <v>333</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Elsagervej 25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H7">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Enghavevej 4B</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">753688, 3150126</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H8">
-        <v>926</v>
+        <v>300</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 12A</t>
+          <t xml:space="preserve">Georg Jensens Vej 10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">402929, 402930</t>
+          <t xml:space="preserve">5524988</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>874</v>
+        <v>335</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,17 +571,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerupvej 485A</t>
+          <t xml:space="preserve">Gl Terpetvej 4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">403345, 403346</t>
+          <t xml:space="preserve">752918, 3161163</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="H10">
-        <v>1366</v>
+        <v>409</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30A</t>
+          <t xml:space="preserve">Grønnevold 10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>1091</v>
+        <v>1490</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30B</t>
+          <t xml:space="preserve">Halvejen 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">752878, 3178982</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30C</t>
+          <t xml:space="preserve">Kystvejen 6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">752897, 3178722</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H13">
-        <v>1132</v>
+        <v>417</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
+          <t xml:space="preserve">Landlyst 8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">409430, 409431</t>
+          <t xml:space="preserve">753043, 5524982</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H14">
-        <v>7175</v>
+        <v>944</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femhøje 5A</t>
+          <t xml:space="preserve">Parallelvej 14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">428228, 428229, 428230</t>
+          <t xml:space="preserve">753689, 9043260</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H15">
-        <v>3279</v>
+        <v>536</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Jensens Vej 10</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524988</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H16">
-        <v>335</v>
+        <v>446</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevold 10</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H17">
-        <v>1490</v>
+        <v>926</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 1</t>
+          <t xml:space="preserve">Skovvejen 5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">752878, 3178982</t>
+          <t xml:space="preserve">100450176</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H18">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystvejen 6</t>
+          <t xml:space="preserve">Strandvejen 78</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">752897, 3178722</t>
+          <t xml:space="preserve">752900, 8528488</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H19">
-        <v>417</v>
+        <v>274</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 78</t>
+          <t xml:space="preserve">Svanelunden 6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">752900, 8528488</t>
+          <t xml:space="preserve">753113, 8719628</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H20">
-        <v>274</v>
+        <v>623</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Terpetvej 4</t>
+          <t xml:space="preserve">Svanelunden 9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">752918, 3161163</t>
+          <t xml:space="preserve">8719628</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="H21">
-        <v>409</v>
+        <v>365</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landlyst 8</t>
+          <t xml:space="preserve">Taagholtvej 178</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">753043, 5524982</t>
+          <t xml:space="preserve">753685, 3168904</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H22">
-        <v>944</v>
+        <v>1666</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelunden 6</t>
+          <t xml:space="preserve">Taagholtvej 184</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">753113, 8719628</t>
+          <t xml:space="preserve">3168907</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>623</v>
+        <v>436</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1471,26 +1471,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 178</t>
+          <t xml:space="preserve">Willemoesvej 4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">753685, 3168904</t>
+          <t xml:space="preserve">3177919, 100507701</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H25">
-        <v>1666</v>
+        <v>3596</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,40 +1531,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 4B</t>
+          <t xml:space="preserve">Nørregade 22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">753688, 3150126</t>
+          <t xml:space="preserve">5521954</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>300</v>
+        <v>3374</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047596</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-04</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 14</t>
+          <t xml:space="preserve">Nørrebro 36</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">753689, 9043260</t>
+          <t xml:space="preserve">3142760</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="H27">
-        <v>536</v>
+        <v>2030</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047760</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1651,40 +1651,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asdalvej 16</t>
+          <t xml:space="preserve">Doggerbanke 12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719163</t>
+          <t xml:space="preserve">3178748</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>1761</v>
+        <v>853</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200048720</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-05-02</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1711,40 +1711,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodøvej 13</t>
+          <t xml:space="preserve">Stendyssevej 80F</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H29">
-        <v>1980</v>
+        <v>1674</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200051322</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-07-13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelunden 9</t>
+          <t xml:space="preserve">Elsagervej 25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719628</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="H30">
-        <v>365</v>
+        <v>1934</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200053550</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-10-04</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baggesvognsvej 1</t>
+          <t xml:space="preserve">Grønnevold 10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9043261</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="H31">
-        <v>418</v>
+        <v>480</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200054733</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1891,40 +1891,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baggesvognsvej 57A</t>
+          <t xml:space="preserve">Vester Hedevej 251</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9598787</t>
+          <t xml:space="preserve">5526510</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200054944</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-11-17</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 22</t>
+          <t xml:space="preserve">Enghavevej 11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521954</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H33">
-        <v>3374</v>
+        <v>779</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047596</t>
+          <t xml:space="preserve">200055336</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-04</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,35 +2011,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 36</t>
+          <t xml:space="preserve">Fuglsigvej 23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3142760</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H34">
-        <v>2030</v>
+        <v>1992</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047760</t>
+          <t xml:space="preserve">200055924</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-07</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doggerbanke 12</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178748</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="H35">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048720</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-02</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80F</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H36">
-        <v>1674</v>
+        <v>470</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051323</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-07-13</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H37">
-        <v>1934</v>
+        <v>1347</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053550</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-04</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,35 +2251,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevold 10</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H38">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054733</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Hedevej 251</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526510</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H39">
-        <v>258</v>
+        <v>575</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054944</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-17</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 11</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>779</v>
+        <v>394</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055336</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,20 +2441,20 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H41">
-        <v>852</v>
+        <v>585</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,20 +2501,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>470</v>
+        <v>1647</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Ulvmosevej 3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3150176</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>1347</v>
+        <v>499</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055998</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,35 +2611,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Jerupvej 485A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">403345, 403346</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>422</v>
+        <v>1366</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200056210</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vendelbogade 10A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3169983</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>575</v>
+        <v>5060</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200056198</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Vrenstedvej 54</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">9980081</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H46">
-        <v>394</v>
+        <v>560</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">311044984</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2024-03-26</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Poulstrup Skolevej 5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">753473, 3217725</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H47">
-        <v>585</v>
+        <v>1765</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">311126737</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2025-07-29</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H48">
-        <v>1647</v>
+        <v>656</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">311132374</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 23</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H49">
-        <v>1992</v>
+        <v>3761</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055924</t>
+          <t xml:space="preserve">311132374</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvmosevej 3</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150176</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H50">
-        <v>499</v>
+        <v>801</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055998</t>
+          <t xml:space="preserve">311132374</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 10A</t>
+          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169983</t>
+          <t xml:space="preserve">3178967</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>5060</v>
+        <v>1631</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056198</t>
+          <t xml:space="preserve">311175796</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-21</t>
+          <t xml:space="preserve">2026-05-11</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,45 +3091,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrenstedvej 54</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980081</t>
+          <t xml:space="preserve">5521204</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>560</v>
+        <v>4153</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311044984</t>
+          <t xml:space="preserve">311213844</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-26</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3151,45 +3151,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poulstrup Skolevej 5</t>
+          <t xml:space="preserve">Amtmandstoften 2A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">753473, 3217725</t>
+          <t xml:space="preserve">5521383</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>1765</v>
+        <v>1332</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311126737</t>
+          <t xml:space="preserve">311224295</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-29</t>
+          <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3211,45 +3211,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Asdalvej 14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">3159619</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>656</v>
+        <v>3719</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311466015</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3271,45 +3271,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>3761</v>
+        <v>2764</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3331,45 +3331,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H56">
-        <v>801</v>
+        <v>1021</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3391,45 +3391,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178967</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H57">
-        <v>1631</v>
+        <v>4161</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311175796</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-11</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521204</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H58">
-        <v>4153</v>
+        <v>808</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213844</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amtmandstoften 2A</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,25 +3521,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521383</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>1332</v>
+        <v>1395</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224295</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-24</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asdalvej 14</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,20 +3581,20 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159619</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H60">
-        <v>3719</v>
+        <v>598</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466015</t>
+          <t xml:space="preserve">311466011</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3646,11 +3646,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H61">
-        <v>1395</v>
+        <v>2086</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3706,15 +3706,15 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H62">
-        <v>598</v>
+        <v>1240</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466011</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3766,11 +3766,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H63">
-        <v>2086</v>
+        <v>1325</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3826,11 +3826,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H64">
-        <v>1240</v>
+        <v>2005</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3886,11 +3886,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H65">
-        <v>1325</v>
+        <v>1055</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H66">
-        <v>2005</v>
+        <v>3691</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H67">
-        <v>1055</v>
+        <v>1680</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,25 +4061,25 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H68">
-        <v>2764</v>
+        <v>1073</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H69">
-        <v>1021</v>
+        <v>1780</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Børge Christensens V 4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">1507102</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>4161</v>
+        <v>6875</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311477652</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Idrætsmarken 15A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,25 +4241,25 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H71">
-        <v>808</v>
+        <v>717</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Vellingshøjvej 380B</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,25 +4301,25 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H72">
-        <v>3691</v>
+        <v>2644</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477664</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Finlandsgade 12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H73">
-        <v>1680</v>
+        <v>464</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311485016</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>1073</v>
+        <v>1477</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311485012</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H75">
-        <v>1780</v>
+        <v>1933</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311485012</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børge Christensens V 4</t>
+          <t xml:space="preserve">Norgesvej 6</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507102</t>
+          <t xml:space="preserve">5524762</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>6875</v>
+        <v>8112</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477652</t>
+          <t xml:space="preserve">311485007</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15A</t>
+          <t xml:space="preserve">Rævskærvej 8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H77">
-        <v>717</v>
+        <v>684</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 380B</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>2644</v>
+        <v>842</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477664</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H79">
-        <v>842</v>
+        <v>919</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4786,11 +4786,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H80">
-        <v>919</v>
+        <v>495</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4846,11 +4846,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H81">
-        <v>495</v>
+        <v>1088</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,20 +4901,20 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H82">
-        <v>1088</v>
+        <v>966</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,30 +4951,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsgade 12</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H83">
-        <v>464</v>
+        <v>1942</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485016</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,30 +5011,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 7</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170022</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H84">
-        <v>3071</v>
+        <v>634</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485008</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H85">
-        <v>1477</v>
+        <v>1974</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,20 +5141,20 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H86">
-        <v>1933</v>
+        <v>668</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5191,30 +5191,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævskærvej 8</t>
+          <t xml:space="preserve">Vendelbogade 7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3170022</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>684</v>
+        <v>3071</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485008</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5251,30 +5251,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vestbakken 12</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3210318</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H88">
-        <v>966</v>
+        <v>785</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485005</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>1942</v>
+        <v>528</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H90">
-        <v>634</v>
+        <v>941</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H91">
-        <v>1974</v>
+        <v>2112</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H92">
-        <v>668</v>
+        <v>458</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestbakken 12</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3210318</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H93">
-        <v>785</v>
+        <v>602</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485005</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 6</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524762</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H94">
-        <v>8112</v>
+        <v>393</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485007</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,30 +5671,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80F</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H95">
-        <v>534</v>
+        <v>440</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485121</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5746,11 +5746,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H96">
-        <v>528</v>
+        <v>812</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5806,11 +5806,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H97">
-        <v>941</v>
+        <v>406</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5866,11 +5866,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H98">
-        <v>2112</v>
+        <v>1230</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5926,11 +5926,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H99">
-        <v>458</v>
+        <v>946</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5986,11 +5986,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H100">
-        <v>602</v>
+        <v>1206</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6031,30 +6031,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Stendyssevej 80F</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H101">
-        <v>393</v>
+        <v>534</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485121</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Aage Holms Vej 6</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">7881176</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>440</v>
+        <v>760</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494575</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Enghavevej 2A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,25 +6161,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>812</v>
+        <v>349</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,25 +6221,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>406</v>
+        <v>886</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H105">
-        <v>1230</v>
+        <v>430</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,25 +6341,25 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H106">
-        <v>946</v>
+        <v>507</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Fuglsigvej 21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">5527904</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>1206</v>
+        <v>586</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494579</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Græshedevej 26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,20 +6461,20 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3204366</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>269</v>
+        <v>536</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494582</t>
+          <t xml:space="preserve">311494576</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6511,30 +6511,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Grønningen 1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H109">
-        <v>415</v>
+        <v>1399</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494581</t>
+          <t xml:space="preserve">311494556</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 137</t>
+          <t xml:space="preserve">H C Andersens Vej 1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800309</t>
+          <t xml:space="preserve">3168485</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,11 +6590,11 @@
         </is>
       </c>
       <c r="H110">
-        <v>549</v>
+        <v>669</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494569</t>
+          <t xml:space="preserve">311494573</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,30 +6631,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 27</t>
+          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H111">
-        <v>2334</v>
+        <v>455</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,30 +6691,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Kingosvej 10</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>3417</v>
+        <v>1336</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6751,30 +6751,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 1</t>
+          <t xml:space="preserve">Lonesvej 192</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">8719671</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>1399</v>
+        <v>707</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494556</t>
+          <t xml:space="preserve">311494577</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2A</t>
+          <t xml:space="preserve">Lundtoftevej 48</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">5527621</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,11 +6830,11 @@
         </is>
       </c>
       <c r="H114">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494568</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6871,30 +6871,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Nørrebro 27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>886</v>
+        <v>2334</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,30 +6931,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Sct Knuds Alle 10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">9797238</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>430</v>
+        <v>766</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494566</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,30 +6991,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>507</v>
+        <v>393</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Andersens Vej 1</t>
+          <t xml:space="preserve">Skagensvej 137</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168485</t>
+          <t xml:space="preserve">1800309</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,11 +7070,11 @@
         </is>
       </c>
       <c r="H118">
-        <v>669</v>
+        <v>549</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494573</t>
+          <t xml:space="preserve">311494569</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7111,30 +7111,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshedevej 26</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204366</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H119">
-        <v>536</v>
+        <v>3417</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494576</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,20 +7181,20 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H120">
-        <v>393</v>
+        <v>269</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kingosvej 10</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,20 +7241,20 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H121">
-        <v>1336</v>
+        <v>415</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494581</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>455</v>
+        <v>8698</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,35 +7351,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 48</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527621</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H123">
-        <v>381</v>
+        <v>1003</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494568</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 21</t>
+          <t xml:space="preserve">Idræts Alle 1</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527904</t>
+          <t xml:space="preserve">100218261</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>586</v>
+        <v>8190</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494579</t>
+          <t xml:space="preserve">311566030</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 6</t>
+          <t xml:space="preserve">Vanggårdsgade 17</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7881176</t>
+          <t xml:space="preserve">3178968</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494575</t>
+          <t xml:space="preserve">311625072</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lonesvej 192</t>
+          <t xml:space="preserve">Palleskær Engvej 5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719671</t>
+          <t xml:space="preserve">5526859</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="H126">
-        <v>707</v>
+        <v>2155</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494577</t>
+          <t xml:space="preserve">311650741</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Knuds Alle 10</t>
+          <t xml:space="preserve">Nordbovej 5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9797238</t>
+          <t xml:space="preserve">5522955</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>766</v>
+        <v>2615</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494566</t>
+          <t xml:space="preserve">311669639</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8</t>
+          <t xml:space="preserve">Hvidegårds Ager 25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">1507298</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>8698</v>
+        <v>395</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311674591</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,35 +7711,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
+          <t xml:space="preserve">Brændingen 2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">3218381</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H129">
-        <v>1003</v>
+        <v>299</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311790590</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 1</t>
+          <t xml:space="preserve">Ved Banen 8</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100218261</t>
+          <t xml:space="preserve">100606984</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>8190</v>
+        <v>10174</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566030</t>
+          <t xml:space="preserve">311794226</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 17</t>
+          <t xml:space="preserve">Brændingen 12A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178968</t>
+          <t xml:space="preserve">402929, 402930</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>751</v>
+        <v>874</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625072</t>
+          <t xml:space="preserve">311885675</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palleskær Engvej 5</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526859</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7910,16 +7910,16 @@
         </is>
       </c>
       <c r="H132">
-        <v>2155</v>
+        <v>2230</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650741</t>
+          <t xml:space="preserve">311885676</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordbovej 5</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522955</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H133">
-        <v>2615</v>
+        <v>1492</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669639</t>
+          <t xml:space="preserve">311885677</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidegårds Ager 25</t>
+          <t xml:space="preserve">Bugten 4</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507298</t>
+          <t xml:space="preserve">3162830</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674591</t>
+          <t xml:space="preserve">311885642</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 2</t>
+          <t xml:space="preserve">Dronningensgade 31</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218381</t>
+          <t xml:space="preserve">5521240</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="H135">
-        <v>299</v>
+        <v>473</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790590</t>
+          <t xml:space="preserve">311885656</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Banen 8</t>
+          <t xml:space="preserve">Fynsgade 13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">100606984</t>
+          <t xml:space="preserve">5521521</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8150,16 +8150,16 @@
         </is>
       </c>
       <c r="H136">
-        <v>10174</v>
+        <v>3681</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794226</t>
+          <t xml:space="preserve">311885649</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugten 4</t>
+          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162830</t>
+          <t xml:space="preserve">3217023</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,11 +8210,11 @@
         </is>
       </c>
       <c r="H137">
-        <v>432</v>
+        <v>269</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885642</t>
+          <t xml:space="preserve">311885687</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 3</t>
+          <t xml:space="preserve">Overgade 7</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178136</t>
+          <t xml:space="preserve">5521462</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8270,11 +8270,11 @@
         </is>
       </c>
       <c r="H138">
-        <v>278</v>
+        <v>667</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885633</t>
+          <t xml:space="preserve">311885657</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20A</t>
+          <t xml:space="preserve">Skagerakvej 3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,20 +8321,20 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3178136</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H139">
-        <v>515</v>
+        <v>278</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885634</t>
+          <t xml:space="preserve">311885633</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
+          <t xml:space="preserve">Svanelundsbakken 25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217023</t>
+          <t xml:space="preserve">5527785</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,11 +8390,11 @@
         </is>
       </c>
       <c r="H140">
-        <v>269</v>
+        <v>4178</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885687</t>
+          <t xml:space="preserve">311885653</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8431,30 +8431,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Søndergade 20A</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H141">
-        <v>2230</v>
+        <v>515</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885676</t>
+          <t xml:space="preserve">311885634</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,35 +8491,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Fuglsigvej 52</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">1808737</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H142">
-        <v>1492</v>
+        <v>402</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885677</t>
+          <t xml:space="preserve">311886408</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 31</t>
+          <t xml:space="preserve">Hirtshalsvej 17</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521240</t>
+          <t xml:space="preserve">7201111</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="H143">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885656</t>
+          <t xml:space="preserve">311886401</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 7</t>
+          <t xml:space="preserve">Tværvej 9A</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521462</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8630,16 +8630,16 @@
         </is>
       </c>
       <c r="H144">
-        <v>667</v>
+        <v>256</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885657</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 13</t>
+          <t xml:space="preserve">Tværvej 9E</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521521</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H145">
-        <v>3681</v>
+        <v>382</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885649</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelundsbakken 25</t>
+          <t xml:space="preserve">Femhøje 5A</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527785</t>
+          <t xml:space="preserve">428228, 428229, 428230</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8750,16 +8750,16 @@
         </is>
       </c>
       <c r="H146">
-        <v>4178</v>
+        <v>3279</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885653</t>
+          <t xml:space="preserve">311886888</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,17 +8791,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 52</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808737</t>
+          <t xml:space="preserve">3214506</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,16 +8810,16 @@
         </is>
       </c>
       <c r="H147">
-        <v>402</v>
+        <v>4371</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886408</t>
+          <t xml:space="preserve">311886892</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,17 +8851,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9A</t>
+          <t xml:space="preserve">Valmuevej 3A</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">3214536</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8870,16 +8870,16 @@
         </is>
       </c>
       <c r="H148">
-        <v>256</v>
+        <v>820</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886893</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,35 +8911,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9E</t>
+          <t xml:space="preserve">Østergade 30A</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">407002</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H149">
-        <v>382</v>
+        <v>1091</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311887712</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,35 +8971,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 17</t>
+          <t xml:space="preserve">Østergade 30B</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7201111</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H150">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886401</t>
+          <t xml:space="preserve">311887713</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,35 +9031,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Østergade 30C</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214506</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H151">
-        <v>4371</v>
+        <v>1132</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886892</t>
+          <t xml:space="preserve">311887715</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,17 +9091,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valmuevej 3A</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214536</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9110,16 +9110,16 @@
         </is>
       </c>
       <c r="H152">
-        <v>820</v>
+        <v>265</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886893</t>
+          <t xml:space="preserve">311888133</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9166,15 +9166,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H153">
-        <v>265</v>
+        <v>393</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888133</t>
+          <t xml:space="preserve">311888130</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,35 +9211,35 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24A</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H154">
-        <v>393</v>
+        <v>1086</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888130</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24A</t>
+          <t xml:space="preserve">Tannisbugtvej 24B</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9286,11 +9286,11 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H155">
-        <v>1086</v>
+        <v>994</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24B</t>
+          <t xml:space="preserve">Tannisbugtvej 24C</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9346,11 +9346,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H156">
-        <v>994</v>
+        <v>611</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9391,30 +9391,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24C</t>
+          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">409430, 409431</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H157">
-        <v>611</v>
+        <v>7175</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888761</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingbanke 12</t>
+          <t xml:space="preserve">Tykskovvej 4</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971909</t>
+          <t xml:space="preserve">9547586</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,11 +9470,11 @@
         </is>
       </c>
       <c r="H158">
-        <v>2534</v>
+        <v>4610</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888727</t>
+          <t xml:space="preserve">311888732</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9511,17 +9511,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tykskovvej 4</t>
+          <t xml:space="preserve">Vikingbanke 12</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547586</t>
+          <t xml:space="preserve">8971909</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9530,11 +9530,11 @@
         </is>
       </c>
       <c r="H159">
-        <v>4610</v>
+        <v>2534</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888732</t>
+          <t xml:space="preserve">311888727</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Albert Ginges Vej 15</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">5525116</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="H160">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892242</t>
+          <t xml:space="preserve">311892238</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagen Landevej 113</t>
+          <t xml:space="preserve">Bøgstedvej 245</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159903</t>
+          <t xml:space="preserve">7007775</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9650,11 +9650,11 @@
         </is>
       </c>
       <c r="H161">
-        <v>752</v>
+        <v>481</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892241</t>
+          <t xml:space="preserve">311892240</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Ginges Vej 15</t>
+          <t xml:space="preserve">Skagen Landevej 113</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525116</t>
+          <t xml:space="preserve">3159903</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,11 +9710,11 @@
         </is>
       </c>
       <c r="H162">
-        <v>360</v>
+        <v>752</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892238</t>
+          <t xml:space="preserve">311892241</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgstedvej 245</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007775</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9770,11 +9770,11 @@
         </is>
       </c>
       <c r="H163">
-        <v>481</v>
+        <v>310</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892240</t>
+          <t xml:space="preserve">311892242</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 8</t>
+          <t xml:space="preserve">Brændingen 4</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">3218373</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H165">
-        <v>337</v>
+        <v>455</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311893154</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftagervej 1</t>
+          <t xml:space="preserve">Sejlstrupvej 8</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177487</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>1813</v>
+        <v>337</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893155</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 4</t>
+          <t xml:space="preserve">Toftagervej 1</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218373</t>
+          <t xml:space="preserve">3177487</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,11 +10010,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>455</v>
+        <v>1813</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893154</t>
+          <t xml:space="preserve">311893155</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894479</t>
+          <t xml:space="preserve">311894481</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10241,20 +10241,20 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H171">
-        <v>857</v>
+        <v>2284</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895836</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,20 +10301,20 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H172">
-        <v>1934</v>
+        <v>5053</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,20 +10361,20 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H173">
-        <v>1420</v>
+        <v>996</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10426,15 +10426,15 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>584</v>
+        <v>857</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311895836</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10481,20 +10481,20 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H175">
-        <v>5053</v>
+        <v>1934</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10541,20 +10541,20 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H176">
-        <v>996</v>
+        <v>1420</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10610,11 +10610,11 @@
         </is>
       </c>
       <c r="H177">
-        <v>2284</v>
+        <v>584</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10771,17 +10771,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr Vråvej 5</t>
+          <t xml:space="preserve">Idræts Alle 45</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214265</t>
+          <t xml:space="preserve">9885530</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -10790,11 +10790,11 @@
         </is>
       </c>
       <c r="H180">
-        <v>2793</v>
+        <v>372</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901495</t>
+          <t xml:space="preserve">311901519</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,17 +10831,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45</t>
+          <t xml:space="preserve">Sdr Vråvej 5</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885530</t>
+          <t xml:space="preserve">3214265</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="H181">
-        <v>372</v>
+        <v>2793</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901519</t>
+          <t xml:space="preserve">311901495</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10891,30 +10891,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 170</t>
+          <t xml:space="preserve">Skolevangen 46</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403213</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H182">
-        <v>407</v>
+        <v>1334</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918197</t>
+          <t xml:space="preserve">311918196</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 15</t>
+          <t xml:space="preserve">Taagholtvej 170</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800354</t>
+          <t xml:space="preserve">1403213</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10970,11 +10970,11 @@
         </is>
       </c>
       <c r="H183">
-        <v>940</v>
+        <v>407</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918198</t>
+          <t xml:space="preserve">311918197</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391A</t>
+          <t xml:space="preserve">Torvegade 15</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3167523</t>
+          <t xml:space="preserve">1800354</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11030,11 +11030,11 @@
         </is>
       </c>
       <c r="H184">
-        <v>427</v>
+        <v>940</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918170</t>
+          <t xml:space="preserve">311918198</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 46</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,20 +11081,20 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H185">
-        <v>1334</v>
+        <v>251</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918196</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11146,11 +11146,11 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H186">
-        <v>251</v>
+        <v>567</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Vellingshøjvej 391A</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,20 +11201,20 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">3167523</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H187">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311918170</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 44</t>
+          <t xml:space="preserve">Elsagervej 27A</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522933</t>
+          <t xml:space="preserve">7871638</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,11 +11330,11 @@
         </is>
       </c>
       <c r="H189">
-        <v>1040</v>
+        <v>1723</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922368</t>
+          <t xml:space="preserve">311922371</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Jensens Vej 12</t>
+          <t xml:space="preserve">Elsagervej 44</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524990</t>
+          <t xml:space="preserve">5522933</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>2910</v>
+        <v>1040</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922280</t>
+          <t xml:space="preserve">311922368</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 8</t>
+          <t xml:space="preserve">Georg Jensens Vej 12</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002365</t>
+          <t xml:space="preserve">5524990</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11450,11 +11450,11 @@
         </is>
       </c>
       <c r="H191">
-        <v>367</v>
+        <v>2910</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922282</t>
+          <t xml:space="preserve">311922280</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 6</t>
+          <t xml:space="preserve">Grønningen 8</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010644</t>
+          <t xml:space="preserve">7002365</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11510,11 +11510,11 @@
         </is>
       </c>
       <c r="H192">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922366</t>
+          <t xml:space="preserve">311922282</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 27A</t>
+          <t xml:space="preserve">Tjørnevej 6</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">7871638</t>
+          <t xml:space="preserve">7010644</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11570,11 +11570,11 @@
         </is>
       </c>
       <c r="H193">
-        <v>1723</v>
+        <v>380</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922371</t>
+          <t xml:space="preserve">311922366</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Thirupvej 55A</t>
+          <t xml:space="preserve">Aage Holms Vej 8</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014113</t>
+          <t xml:space="preserve">9938684</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11630,11 +11630,11 @@
         </is>
       </c>
       <c r="H194">
-        <v>448</v>
+        <v>4353</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922665</t>
+          <t xml:space="preserve">311922647</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 8</t>
+          <t xml:space="preserve">Vester Thirupvej 55A</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9938684</t>
+          <t xml:space="preserve">10014113</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -11750,11 +11750,11 @@
         </is>
       </c>
       <c r="H196">
-        <v>4353</v>
+        <v>448</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922647</t>
+          <t xml:space="preserve">311922665</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">

--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132374</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132374</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132374</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">

--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -1734,7 +1734,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051322</t>
+          <t xml:space="preserve">200051323</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311132374</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311132374</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311132374</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485012</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485012</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494580</t>
+          <t xml:space="preserve">311494582</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894481</t>
+          <t xml:space="preserve">311894479</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">

--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:M197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-04</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-05-02</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1734,20 +1874,25 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051323</t>
+          <t xml:space="preserve">200051322</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-07-13</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-04</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-17</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-03-26</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-07-29</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2874,20 +3109,25 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132374</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2934,20 +3174,25 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132374</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2994,20 +3239,25 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132374</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-11</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygge-syn ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-14</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-30</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,21 +12799,26 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L197"/>
+  <autoFilter ref="A1:M197"/>
 </worksheet>
 </file>
--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -6684,7 +6684,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494582</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
